--- a/model/Output_Budget/5. Prosumer percentage/Base Cases/100/Output_0_40.xlsx
+++ b/model/Output_Budget/5. Prosumer percentage/Base Cases/100/Output_0_40.xlsx
@@ -496,7 +496,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1192870.454836786</v>
+        <v>1192870.454836785</v>
       </c>
     </row>
     <row r="7">
@@ -26285,22 +26285,22 @@
         <v>525790.9199777954</v>
       </c>
       <c r="J2" t="n">
-        <v>436303.3390498925</v>
+        <v>436303.3390498926</v>
       </c>
       <c r="K2" t="n">
         <v>523898.4668372231</v>
       </c>
       <c r="L2" t="n">
-        <v>533744.1012751701</v>
+        <v>533744.10127517</v>
       </c>
       <c r="M2" t="n">
-        <v>533744.1012751701</v>
+        <v>533744.10127517</v>
       </c>
       <c r="N2" t="n">
-        <v>533744.1012751701</v>
+        <v>533744.10127517</v>
       </c>
       <c r="O2" t="n">
-        <v>436303.3390498925</v>
+        <v>436303.3390498926</v>
       </c>
       <c r="P2" t="n">
         <v>247538.5746241431</v>
@@ -26374,19 +26374,19 @@
         <v>299023.995811336</v>
       </c>
       <c r="E4" t="n">
-        <v>280081.5545038176</v>
+        <v>280081.5545038177</v>
       </c>
       <c r="F4" t="n">
-        <v>297779.8398421858</v>
+        <v>297779.839842186</v>
       </c>
       <c r="G4" t="n">
-        <v>300104.1457560302</v>
+        <v>300104.1457560303</v>
       </c>
       <c r="H4" t="n">
-        <v>300104.1457560302</v>
+        <v>300104.1457560303</v>
       </c>
       <c r="I4" t="n">
-        <v>300104.1457560302</v>
+        <v>300104.1457560303</v>
       </c>
       <c r="J4" t="n">
         <v>249027.5808901401</v>
@@ -26407,7 +26407,7 @@
         <v>249027.5808901401</v>
       </c>
       <c r="P4" t="n">
-        <v>141286.8683285383</v>
+        <v>141286.8683285384</v>
       </c>
     </row>
     <row r="5">
@@ -26472,16 +26472,16 @@
         <v>190533.515711704</v>
       </c>
       <c r="C6" t="n">
-        <v>191179.0357461657</v>
+        <v>191179.0357461656</v>
       </c>
       <c r="D6" t="n">
-        <v>191179.0357461657</v>
+        <v>191179.0357461656</v>
       </c>
       <c r="E6" t="n">
-        <v>-102207.2006996251</v>
+        <v>-102207.2006996253</v>
       </c>
       <c r="F6" t="n">
-        <v>156296.0085376334</v>
+        <v>156296.0085376333</v>
       </c>
       <c r="G6" t="n">
         <v>185604.7625949733</v>
@@ -26493,25 +26493,25 @@
         <v>191705.8101497344</v>
       </c>
       <c r="J6" t="n">
-        <v>-25442.93183093877</v>
+        <v>-25442.93183093875</v>
       </c>
       <c r="K6" t="n">
-        <v>65289.43912335649</v>
+        <v>65289.43912335643</v>
       </c>
       <c r="L6" t="n">
-        <v>170535.5613390426</v>
+        <v>170535.5613390425</v>
       </c>
       <c r="M6" t="n">
-        <v>193620.348683389</v>
+        <v>193620.3486833889</v>
       </c>
       <c r="N6" t="n">
-        <v>193620.348683389</v>
+        <v>193620.3486833889</v>
       </c>
       <c r="O6" t="n">
-        <v>83195.24558413547</v>
+        <v>83195.24558413548</v>
       </c>
       <c r="P6" t="n">
-        <v>95417.1577849086</v>
+        <v>95417.15778490853</v>
       </c>
     </row>
   </sheetData>
